--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhatt\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{922CFFD7-E3DC-4226-B42C-37E6EF529CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF4E53E-DB06-4CDA-997F-004A1F2F8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Notices" sheetId="1" r:id="rId1"/>
-    <sheet name="Results" sheetId="2" r:id="rId2"/>
+    <sheet name="GeneralNotices" sheetId="4" r:id="rId1"/>
+    <sheet name="Holidays" sheetId="3" r:id="rId2"/>
+    <sheet name="ExamNotices" sheetId="1" r:id="rId3"/>
+    <sheet name="Results" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>title</t>
   </si>
@@ -79,13 +81,58 @@
   </si>
   <si>
     <t>https://bbhatt.com.np</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>Mock Data 1</t>
+  </si>
+  <si>
+    <t>Mock Data 2</t>
+  </si>
+  <si>
+    <t>Mock Data 3</t>
+  </si>
+  <si>
+    <t>Bell</t>
+  </si>
+  <si>
+    <t>FileText</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>2082-02-02 to 2082-02-03</t>
+  </si>
+  <si>
+    <t>2082-02-02 to 2082-02-04</t>
+  </si>
+  <si>
+    <t>2082-02-02 to 2082-02-05</t>
+  </si>
+  <si>
+    <t>Calendar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +144,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,8 +178,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -461,18 +514,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14FC3B3-2AAB-4D6A-9BA6-A195DDD1C4A1}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820D46FA-ACC3-4246-8664-7204E505C772}">
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>66782</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>66783</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>66784</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A85314-165E-4808-847D-10018C6DFF73}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14FC3B3-2AAB-4D6A-9BA6-A195DDD1C4A1}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -486,25 +669,54 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>66782</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>66783</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>66784</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{CE314454-4769-4F63-A0BB-91C460B4A6A0}"/>
+    <hyperlink ref="D3:D4" r:id="rId2" display="https://bbhatt.com.np" xr:uid="{1ECD11F9-3B95-49F2-9071-6DD1FE081E54}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC53C596-5529-4790-AB27-E412B3A7F756}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhatt\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF4E53E-DB06-4CDA-997F-004A1F2F8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FC2F48-7631-420C-AB2C-2DC8A149E6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralNotices" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>title</t>
   </si>
@@ -123,6 +123,30 @@
   </si>
   <si>
     <t>Calendar</t>
+  </si>
+  <si>
+    <t>Mock Data 4</t>
+  </si>
+  <si>
+    <t>Mock Data 5</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>DOB</t>
   </si>
 </sst>
 </file>
@@ -718,13 +742,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC53C596-5529-4790-AB27-E412B3A7F756}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -732,33 +757,120 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>83035</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2">
+        <v>60411</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>83036</v>
+      </c>
+      <c r="C3" s="2">
+        <v>60412</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>5.3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>83037</v>
+      </c>
+      <c r="C4" s="2">
+        <v>60413</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>83038</v>
+      </c>
+      <c r="C5" s="2">
+        <v>60414</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>3.3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>83039</v>
+      </c>
+      <c r="C6" s="2">
+        <v>60415</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhatt\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FC2F48-7631-420C-AB2C-2DC8A149E6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA528C63-066B-4DF3-86AD-2F46F16B2140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralNotices" sheetId="4" r:id="rId1"/>
@@ -113,15 +113,6 @@
     <t>…</t>
   </si>
   <si>
-    <t>2082-02-02 to 2082-02-03</t>
-  </si>
-  <si>
-    <t>2082-02-02 to 2082-02-04</t>
-  </si>
-  <si>
-    <t>2082-02-02 to 2082-02-05</t>
-  </si>
-  <si>
     <t>Calendar</t>
   </si>
   <si>
@@ -147,6 +138,15 @@
   </si>
   <si>
     <t>DOB</t>
+  </si>
+  <si>
+    <t>4 to 8 Falugun, 2082</t>
+  </si>
+  <si>
+    <t>5 to 8 Falugun, 2082</t>
+  </si>
+  <si>
+    <t>6 to 8 Falugun, 2082</t>
   </si>
 </sst>
 </file>
@@ -599,7 +599,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -644,7 +644,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
@@ -655,7 +655,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -757,7 +757,7 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
@@ -800,13 +800,13 @@
         <v>60412</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>5.3</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -820,18 +820,18 @@
         <v>60413</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>2.2000000000000002</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>83038</v>
@@ -840,7 +840,7 @@
         <v>60414</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>3.3</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>83039</v>
@@ -860,7 +860,7 @@
         <v>60415</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>2.2000000000000002</v>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhatt\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA528C63-066B-4DF3-86AD-2F46F16B2140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75F7D18-D8F3-4A92-8C11-ECF7976B5315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{4F6E8338-436D-42B2-9008-EDFC726C3FE2}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralNotices" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>title</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>6 to 8 Falugun, 2082</t>
+  </si>
+  <si>
+    <t>MockData 1 detailed description …</t>
   </si>
 </sst>
 </file>
@@ -154,7 +157,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -203,7 +206,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -539,14 +542,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820D46FA-ACC3-4246-8664-7204E505C772}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -559,8 +562,11 @@
       <c r="D1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -573,8 +579,11 @@
       <c r="D2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -587,8 +596,11 @@
       <c r="D3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -600,6 +612,9 @@
       </c>
       <c r="D4" t="s">
         <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="GeneralNotices" sheetId="1" r:id="rId1"/>
     <sheet name="Holidays" sheetId="2" r:id="rId2"/>
@@ -536,7 +536,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -556,7 +556,7 @@
       <c r="A2" t="str">
         <v>Mock Data</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>66782</v>
       </c>
       <c r="C2" t="str">
@@ -570,7 +570,7 @@
       <c r="A3" t="str">
         <v>Mock Data</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>66783</v>
       </c>
       <c r="C3" t="str">
@@ -584,7 +584,7 @@
       <c r="A4" t="str">
         <v>Mock Data</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>66784</v>
       </c>
       <c r="C4" t="str">
@@ -594,15 +594,23 @@
         <v>https://bbhatt.com.np</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Mock Data</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2082-05-24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Routine</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://bbhatt.com.np</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="D4" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -643,17 +643,17 @@
       <c r="A2" t="str">
         <v>Mock Data 1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>83035</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="str">
         <v>60411</v>
       </c>
       <c r="D2" t="str">
         <v>A+</v>
       </c>
-      <c r="E2">
-        <v>9.7</v>
+      <c r="E2" t="str">
+        <v>4</v>
       </c>
       <c r="F2" t="str">
         <v>Pass</v>
@@ -663,56 +663,56 @@
       <c r="A3" t="str">
         <v>Mock Data 2</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>83036</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="str">
         <v>60412</v>
       </c>
       <c r="D3" t="str">
-        <v>A</v>
-      </c>
-      <c r="E3">
-        <v>5.3</v>
+        <v>B+</v>
+      </c>
+      <c r="E3" t="str">
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>Mock Data 3</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>83037</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="str">
         <v>60413</v>
       </c>
       <c r="D4" t="str">
-        <v>B</v>
-      </c>
-      <c r="E4">
-        <v>2.2</v>
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>Fail</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>Mock Data 4</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>83038</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="str">
         <v>60414</v>
       </c>
       <c r="D5" t="str">
         <v>C</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="str">
         <v>3.3</v>
       </c>
       <c r="F5" t="str">
@@ -723,16 +723,16 @@
       <c r="A6" t="str">
         <v>Mock Data 5</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>83039</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="str">
         <v>60415</v>
       </c>
       <c r="D6" t="str">
         <v>B+</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="str">
         <v>2.2</v>
       </c>
       <c r="F6" t="str">
@@ -740,7 +740,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,16 +422,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mock Data 1</v>
-      </c>
-      <c r="B2">
-        <v>66782</v>
+        <v>Mock Data 2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>66783</v>
       </c>
       <c r="C2" t="str">
-        <v>…ello</v>
+        <v>…</v>
       </c>
       <c r="D2" t="str">
-        <v>Bell</v>
+        <v>FileText</v>
       </c>
       <c r="E2" t="str">
         <v>MockData 1 detailed description …</v>
@@ -439,48 +439,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mock Data 2</v>
-      </c>
-      <c r="B3">
-        <v>66783</v>
+        <v>Mock Data 3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>66784</v>
       </c>
       <c r="C3" t="str">
         <v>…</v>
       </c>
       <c r="D3" t="str">
-        <v>FileText</v>
+        <v>Calendar</v>
       </c>
       <c r="E3" t="str">
         <v>MockData 1 detailed description …</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B4">
-        <v>66784</v>
-      </c>
-      <c r="C4" t="str">
-        <v>…</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="E4" t="str">
-        <v>MockData 1 detailed description …</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,43 +476,9 @@
         <v>details</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data 1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>4 to 8 Falugun, 2082</v>
-      </c>
-      <c r="C2" t="str">
-        <v>…</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data 2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>5 to 8 Falugun, 2082</v>
-      </c>
-      <c r="C3" t="str">
-        <v>…</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>6 to 8 Falugun, 2082</v>
-      </c>
-      <c r="C4" t="str">
-        <v>…</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,41 +422,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mock Data 2</v>
+        <v>ANNUAL FUNCTION 2082</v>
       </c>
       <c r="B2" t="str">
-        <v>66783</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>…</v>
+        <v>We are excited to announce the Annual Function 2082, a day dedicated to celebrating student talent and academic excellence. All students and staff are invited to join the festivities and honor our collective achievements.</v>
       </c>
       <c r="D2" t="str">
-        <v>FileText</v>
+        <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v>MockData 1 detailed description …</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B3" t="str">
-        <v>66784</v>
-      </c>
-      <c r="C3" t="str">
-        <v>…</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="E3" t="str">
-        <v>MockData 1 detailed description …</v>
+        <v>This notice serves to inform all students, faculty, and staff that the college’s most anticipated event of the year—the Annual Function—is scheduled for Falgun 07, 2082. This day is dedicated to celebrating our academic achievements, showcasing student talent, and fostering community spirit. Classes will remain suspended on this day to allow full participation in the festivities.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -485,7 +468,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -501,72 +484,16 @@
         <v>link</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B2" t="str">
-        <v>66782</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D2" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B3" t="str">
-        <v>66783</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D3" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B4" t="str">
-        <v>66784</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D4" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2082-05-24</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D5" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -588,109 +515,9 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data 1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>83035</v>
-      </c>
-      <c r="C2" t="str">
-        <v>60411</v>
-      </c>
-      <c r="D2" t="str">
-        <v>A+</v>
-      </c>
-      <c r="E2" t="str">
-        <v>4</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data 2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>83036</v>
-      </c>
-      <c r="C3" t="str">
-        <v>60412</v>
-      </c>
-      <c r="D3" t="str">
-        <v>B+</v>
-      </c>
-      <c r="E3" t="str">
-        <v>3</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>83037</v>
-      </c>
-      <c r="C4" t="str">
-        <v>60413</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Mock Data 4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>83038</v>
-      </c>
-      <c r="C5" t="str">
-        <v>60414</v>
-      </c>
-      <c r="D5" t="str">
-        <v>C</v>
-      </c>
-      <c r="E5" t="str">
-        <v>3.3</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Mock Data 5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>83039</v>
-      </c>
-      <c r="C6" t="str">
-        <v>60415</v>
-      </c>
-      <c r="D6" t="str">
-        <v>B+</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2.2</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -68,9 +68,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,84 +420,16 @@
         <v>details</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data 1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2082-11-02</v>
-      </c>
-      <c r="C2" t="str">
-        <v>…</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Bell</v>
-      </c>
-      <c r="E2" t="str">
-        <v>MockData 1 detailed description …</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data 2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2082-11-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>…</v>
-      </c>
-      <c r="D3" t="str">
-        <v>FileText</v>
-      </c>
-      <c r="E3" t="str">
-        <v>MockData 1 detailed description …</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2082-11-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>…</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Calendar</v>
-      </c>
-      <c r="E4" t="str">
-        <v>MockData 1 detailed description …</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Annuals Fo</v>
-      </c>
-      <c r="B5" t="str">
-        <v>387293</v>
-      </c>
-      <c r="C5" t="str">
-        <v>3987</v>
-      </c>
-      <c r="D5" t="str">
-        <v>dc</v>
-      </c>
-      <c r="E5" t="str">
-        <v>3279872</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -511,50 +442,16 @@
         <v>details</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data 1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>4 to 8 Falugun, 2082</v>
-      </c>
-      <c r="C2" t="str">
-        <v>…</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data 2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>5 to 8 Falugun, 2082</v>
-      </c>
-      <c r="C3" t="str">
-        <v>…</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>6 to 8 Falugun, 2082</v>
-      </c>
-      <c r="C4" t="str">
-        <v>…</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -570,64 +467,16 @@
         <v>link</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B2" s="1">
-        <v>66782</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D2" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B3" s="1">
-        <v>66783</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D3" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data</v>
-      </c>
-      <c r="B4" s="1">
-        <v>66784</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Routine</v>
-      </c>
-      <c r="D4" t="str">
-        <v>https://bbhatt.com.np</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="D4" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -649,110 +498,9 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mock Data 1</v>
-      </c>
-      <c r="B2">
-        <v>83035</v>
-      </c>
-      <c r="C2" s="1">
-        <v>60411</v>
-      </c>
-      <c r="D2" t="str">
-        <v>A+</v>
-      </c>
-      <c r="E2">
-        <v>9.7</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Mock Data 2</v>
-      </c>
-      <c r="B3">
-        <v>83036</v>
-      </c>
-      <c r="C3" s="1">
-        <v>60412</v>
-      </c>
-      <c r="D3" t="str">
-        <v>A</v>
-      </c>
-      <c r="E3">
-        <v>5.3</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Fail</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Mock Data 3</v>
-      </c>
-      <c r="B4">
-        <v>83037</v>
-      </c>
-      <c r="C4" s="1">
-        <v>60413</v>
-      </c>
-      <c r="D4" t="str">
-        <v>B</v>
-      </c>
-      <c r="E4">
-        <v>2.2</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Fail</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Mock Data 4</v>
-      </c>
-      <c r="B5">
-        <v>83038</v>
-      </c>
-      <c r="C5" s="1">
-        <v>60414</v>
-      </c>
-      <c r="D5" t="str">
-        <v>C</v>
-      </c>
-      <c r="E5">
-        <v>3.3</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Mock Data 5</v>
-      </c>
-      <c r="B6">
-        <v>83039</v>
-      </c>
-      <c r="C6" s="1">
-        <v>60415</v>
-      </c>
-      <c r="D6" t="str">
-        <v>B+</v>
-      </c>
-      <c r="E6">
-        <v>2.2</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Pass</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,9 +420,43 @@
         <v>details</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Mock Data 3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2082-11-04</v>
+      </c>
+      <c r="C2" t="str">
+        <v>…</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E2" t="str">
+        <v>MockData 1 detailed description …</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Annuals Fo</v>
+      </c>
+      <c r="B3" t="str">
+        <v>387293</v>
+      </c>
+      <c r="C3" t="str">
+        <v>3987</v>
+      </c>
+      <c r="D3" t="str">
+        <v>dc</v>
+      </c>
+      <c r="E3" t="str">
+        <v>3279872</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/data/notice.xlsx
+++ b/public/data/notice.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,26 +437,9 @@
         <v>MockData 1 detailed description …</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Annuals Fo</v>
-      </c>
-      <c r="B3" t="str">
-        <v>387293</v>
-      </c>
-      <c r="C3" t="str">
-        <v>3987</v>
-      </c>
-      <c r="D3" t="str">
-        <v>dc</v>
-      </c>
-      <c r="E3" t="str">
-        <v>3279872</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
